--- a/eval/mesh_convergence_study.xlsx
+++ b/eval/mesh_convergence_study.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ian-g8\projects\FinalTop\eval\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ian-g8\projects\FinalTop\eval_10x\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15DADBC-18C0-4B04-9AF9-0FE4EB7BED41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75934EFE-1F3E-4F32-B5A2-D136FC143840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{2C2BF513-5EB9-40D0-BBE6-36FCA4731390}"/>
   </bookViews>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Test</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="9">
   <si>
     <t>Beam_loadStep</t>
   </si>
@@ -63,6 +60,12 @@
   </si>
   <si>
     <t>Wheel</t>
+  </si>
+  <si>
+    <t>Test L=1</t>
+  </si>
+  <si>
+    <t>Test L=10</t>
   </si>
 </sst>
 </file>
@@ -454,30 +457,43 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C340CCC-5543-44D0-82D2-9DA8F5FDFC4A}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
       </c>
       <c r="B3">
         <v>0.02</v>
@@ -485,8 +501,17 @@
       <c r="C3">
         <v>0.6734</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0.2</v>
+      </c>
+      <c r="I3">
+        <v>8.8567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>1.4999999999999999E-2</v>
       </c>
@@ -497,8 +522,18 @@
         <f>ABS((C4-C3)/C4)</f>
         <v>0.13411341134113405</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H4">
+        <v>0.15</v>
+      </c>
+      <c r="I4">
+        <v>7.7618999999999998</v>
+      </c>
+      <c r="J4" s="1">
+        <f>ABS((I4-I3)/I4)</f>
+        <v>0.14104793929321432</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>0.01</v>
       </c>
@@ -509,8 +544,18 @@
         <f t="shared" ref="D5:D21" si="0">ABS((C5-C4)/C5)</f>
         <v>8.7206572769953097E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H5">
+        <v>0.1</v>
+      </c>
+      <c r="I5">
+        <v>9.1475000000000009</v>
+      </c>
+      <c r="J5" s="1">
+        <f t="shared" ref="J5:J10" si="1">ABS((I5-I4)/I5)</f>
+        <v>0.15147308007652374</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -521,8 +566,18 @@
         <f t="shared" si="0"/>
         <v>7.5510801983528511E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H6" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="I6">
+        <v>9.2286000000000001</v>
+      </c>
+      <c r="J6" s="1">
+        <f t="shared" si="1"/>
+        <v>8.7878984894782831E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -533,13 +588,24 @@
         <f t="shared" si="0"/>
         <v>5.2356592022164581E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H7">
+        <v>0.06</v>
+      </c>
+      <c r="I7">
+        <v>9.1698000000000004</v>
+      </c>
+      <c r="J7" s="1">
+        <f t="shared" si="1"/>
+        <v>6.4123535954982375E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9">
         <v>0.01</v>
@@ -548,8 +614,18 @@
         <v>0.35870000000000002</v>
       </c>
       <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9">
+        <v>0.15</v>
+      </c>
+      <c r="I9">
+        <v>2.9070999999999998</v>
+      </c>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -560,8 +636,18 @@
         <f t="shared" si="0"/>
         <v>0.17178480720387895</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H10">
+        <v>0.1</v>
+      </c>
+      <c r="I10">
+        <v>4.3224</v>
+      </c>
+      <c r="J10" s="1">
+        <f t="shared" si="1"/>
+        <v>0.32743383305570983</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -572,8 +658,18 @@
         <f t="shared" si="0"/>
         <v>4.6868579439704051E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H11" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="I11">
+        <v>4.3592000000000004</v>
+      </c>
+      <c r="J11" s="1">
+        <f>ABS((I11-I10)/I11)</f>
+        <v>8.4419159478804334E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>4.4999999999999997E-3</v>
       </c>
@@ -584,13 +680,24 @@
         <f t="shared" si="0"/>
         <v>3.7368825185564288E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H12">
+        <v>0.06</v>
+      </c>
+      <c r="I12">
+        <v>4.1401000000000003</v>
+      </c>
+      <c r="J12" s="1">
+        <f>ABS((I12-I11)/I12)</f>
+        <v>5.2921427018671058E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D13" s="1"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14">
         <v>0.01</v>
@@ -599,8 +706,18 @@
         <v>1.788</v>
       </c>
       <c r="D14" s="1"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14">
+        <v>0.1</v>
+      </c>
+      <c r="I14">
+        <v>17.867999999999999</v>
+      </c>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -611,8 +728,18 @@
         <f t="shared" si="0"/>
         <v>3.2886196451752468E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H15" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="I15">
+        <v>18.475999999999999</v>
+      </c>
+      <c r="J15" s="1">
+        <f t="shared" ref="J15:J16" si="2">ABS((I15-I14)/I15)</f>
+        <v>3.2907555747997433E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -623,13 +750,24 @@
         <f t="shared" si="0"/>
         <v>2.432846060478127E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H16">
+        <v>0.06</v>
+      </c>
+      <c r="I16">
+        <v>19.004000000000001</v>
+      </c>
+      <c r="J16" s="1">
+        <f t="shared" si="2"/>
+        <v>2.7783624500105356E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="D17" s="1"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18">
         <v>0.01</v>
@@ -638,8 +776,18 @@
         <v>0.66759999999999997</v>
       </c>
       <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="G18" t="s">
+        <v>6</v>
+      </c>
+      <c r="H18">
+        <v>0.1</v>
+      </c>
+      <c r="I18">
+        <v>6.7290000000000001</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>8.0000000000000002E-3</v>
       </c>
@@ -650,8 +798,18 @@
         <f t="shared" si="0"/>
         <v>7.0453912559175685E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H19">
+        <v>0.08</v>
+      </c>
+      <c r="I19">
+        <v>7.1574999999999998</v>
+      </c>
+      <c r="J19" s="1">
+        <f t="shared" ref="J19:J21" si="3">ABS((I19-I18)/I19)</f>
+        <v>5.9867272092210919E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>6.0000000000000001E-3</v>
       </c>
@@ -662,8 +820,18 @@
         <f t="shared" si="0"/>
         <v>0.10526971471284417</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="H20" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="I20">
+        <v>8.0195000000000007</v>
+      </c>
+      <c r="J20" s="1">
+        <f t="shared" si="3"/>
+        <v>0.10748799800486326</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>4.4999999999999997E-3</v>
       </c>
@@ -673,6 +841,16 @@
       <c r="D21" s="1">
         <f t="shared" si="0"/>
         <v>9.4315895372232787E-3</v>
+      </c>
+      <c r="H21">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="I21">
+        <v>7.9569000000000001</v>
+      </c>
+      <c r="J21" s="1">
+        <f t="shared" si="3"/>
+        <v>7.8673855395946478E-3</v>
       </c>
     </row>
   </sheetData>
